--- a/Input/GoodnessOfFit.Rat.xlsx
+++ b/Input/GoodnessOfFit.Rat.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wageningenur4.sharepoint.com/sites/PARCProjectChrysanthi-CChannel/Gedeelde documenten/Chrysa.Nynke_private/CP_L_R/PBK_ZEARALENONE/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="126" documentId="8_{F350443E-DEEE-42B1-90CB-6C99E0D56984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4655770-FA65-48E3-AD47-8CC4D5B73A7B}"/>
+  <xr:revisionPtr revIDLastSave="128" documentId="8_{F350443E-DEEE-42B1-90CB-6C99E0D56984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E627F534-C141-41A0-A53B-227552234EF2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7A6CC22C-5805-4016-ACC6-80411866AB2B}"/>
   </bookViews>
@@ -1150,6 +1150,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81B64A6D-C161-42B0-BDCE-B401913E74B1}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AD285"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1263,7 +1264,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -1355,7 +1356,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -1447,7 +1448,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -1539,7 +1540,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -1631,7 +1632,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -1723,7 +1724,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -1815,7 +1816,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -1907,7 +1908,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -1999,7 +2000,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -2091,7 +2092,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -2183,7 +2184,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -2275,7 +2276,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -2367,7 +2368,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -2459,7 +2460,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -2551,7 +2552,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -2643,7 +2644,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -2735,7 +2736,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -2827,7 +2828,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -2919,7 +2920,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -3011,7 +3012,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -3103,7 +3104,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -3195,7 +3196,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -3287,7 +3288,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -3379,7 +3380,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -3471,7 +3472,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -3563,7 +3564,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>33</v>
       </c>
@@ -3655,7 +3656,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -3747,7 +3748,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -3839,7 +3840,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>41</v>
       </c>
@@ -3931,7 +3932,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>41</v>
       </c>
@@ -4023,7 +4024,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>41</v>
       </c>
@@ -4115,7 +4116,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -4207,7 +4208,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>41</v>
       </c>
@@ -4299,7 +4300,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>41</v>
       </c>
@@ -4391,7 +4392,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -4483,7 +4484,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -4575,7 +4576,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -4667,7 +4668,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -4759,7 +4760,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>41</v>
       </c>
@@ -4851,7 +4852,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>41</v>
       </c>
@@ -4943,7 +4944,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -5035,7 +5036,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -5127,7 +5128,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>41</v>
       </c>
@@ -5219,7 +5220,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>41</v>
       </c>
@@ -5311,7 +5312,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>41</v>
       </c>
@@ -5403,7 +5404,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>41</v>
       </c>
@@ -5495,7 +5496,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>41</v>
       </c>
@@ -5587,7 +5588,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>41</v>
       </c>
@@ -5679,7 +5680,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>41</v>
       </c>
@@ -5771,7 +5772,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>41</v>
       </c>
@@ -5863,7 +5864,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>41</v>
       </c>
@@ -5955,7 +5956,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>41</v>
       </c>
@@ -6047,7 +6048,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>41</v>
       </c>
@@ -6139,7 +6140,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>41</v>
       </c>
@@ -6231,7 +6232,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>41</v>
       </c>
@@ -6323,7 +6324,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>41</v>
       </c>
@@ -6415,7 +6416,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>41</v>
       </c>
@@ -6507,7 +6508,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>41</v>
       </c>
@@ -6599,7 +6600,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>41</v>
       </c>
@@ -8255,7 +8256,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>66</v>
       </c>
@@ -8347,7 +8348,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="79" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>66</v>
       </c>
@@ -8439,7 +8440,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>66</v>
       </c>
@@ -8531,7 +8532,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="81" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>66</v>
       </c>
@@ -8623,7 +8624,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="82" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>66</v>
       </c>
@@ -8715,7 +8716,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>66</v>
       </c>
@@ -8807,7 +8808,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="84" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>66</v>
       </c>
@@ -8899,7 +8900,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="85" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>66</v>
       </c>
@@ -8991,7 +8992,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="86" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>66</v>
       </c>
@@ -9083,7 +9084,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="87" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>66</v>
       </c>
@@ -9175,7 +9176,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="88" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>66</v>
       </c>
@@ -9267,7 +9268,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>66</v>
       </c>
@@ -9359,7 +9360,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="90" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>66</v>
       </c>
@@ -9451,7 +9452,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="91" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>66</v>
       </c>
@@ -9543,7 +9544,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>66</v>
       </c>
@@ -9635,7 +9636,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>66</v>
       </c>
@@ -9727,7 +9728,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>66</v>
       </c>
@@ -9819,7 +9820,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="95" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>66</v>
       </c>
@@ -9911,7 +9912,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="96" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>66</v>
       </c>
@@ -10003,7 +10004,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="97" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>66</v>
       </c>
@@ -10095,7 +10096,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="98" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>66</v>
       </c>
@@ -10187,7 +10188,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="99" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>66</v>
       </c>
@@ -10279,7 +10280,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="100" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>66</v>
       </c>
@@ -10371,7 +10372,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="101" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>66</v>
       </c>
@@ -10463,7 +10464,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="102" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>66</v>
       </c>
@@ -10555,7 +10556,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="103" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>66</v>
       </c>
@@ -10647,7 +10648,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="104" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>66</v>
       </c>
@@ -10739,7 +10740,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="105" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>66</v>
       </c>
@@ -10831,7 +10832,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="106" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>66</v>
       </c>
@@ -10923,7 +10924,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="107" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>66</v>
       </c>
@@ -11015,7 +11016,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="108" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>66</v>
       </c>
@@ -11107,7 +11108,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="109" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>66</v>
       </c>
@@ -11199,7 +11200,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="110" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>66</v>
       </c>
@@ -11291,7 +11292,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="111" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>66</v>
       </c>
@@ -11383,7 +11384,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="112" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>66</v>
       </c>
@@ -11475,7 +11476,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="113" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>66</v>
       </c>
@@ -11567,7 +11568,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="114" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>66</v>
       </c>
@@ -11659,7 +11660,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="115" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>66</v>
       </c>
@@ -11751,7 +11752,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="116" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>66</v>
       </c>
@@ -11843,7 +11844,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="117" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>66</v>
       </c>
@@ -11935,7 +11936,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="118" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>66</v>
       </c>
@@ -12027,7 +12028,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="119" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>66</v>
       </c>
@@ -12119,7 +12120,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="120" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>66</v>
       </c>
@@ -12211,7 +12212,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="121" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>66</v>
       </c>
@@ -12303,7 +12304,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="122" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>66</v>
       </c>
@@ -12395,7 +12396,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="123" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>66</v>
       </c>
@@ -12487,7 +12488,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="124" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>66</v>
       </c>
@@ -12579,7 +12580,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="125" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>66</v>
       </c>
@@ -12671,7 +12672,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="126" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>66</v>
       </c>
@@ -12763,7 +12764,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="127" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>66</v>
       </c>
@@ -12855,7 +12856,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="128" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>66</v>
       </c>
@@ -12947,7 +12948,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="129" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>66</v>
       </c>
@@ -13039,7 +13040,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="130" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>66</v>
       </c>
@@ -13131,7 +13132,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="131" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>66</v>
       </c>
@@ -13223,7 +13224,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="132" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>66</v>
       </c>
@@ -13315,7 +13316,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="133" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>66</v>
       </c>
@@ -13407,7 +13408,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="134" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>66</v>
       </c>
@@ -13499,7 +13500,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="135" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>66</v>
       </c>
@@ -13591,7 +13592,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="136" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>66</v>
       </c>
@@ -13683,7 +13684,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="137" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>66</v>
       </c>
@@ -13775,7 +13776,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="138" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>66</v>
       </c>
@@ -13867,7 +13868,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="139" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>66</v>
       </c>
@@ -13959,7 +13960,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="140" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>66</v>
       </c>
@@ -14051,7 +14052,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="141" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>66</v>
       </c>
@@ -14143,7 +14144,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="142" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>66</v>
       </c>
@@ -14235,7 +14236,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="143" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>66</v>
       </c>
@@ -14327,7 +14328,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="144" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>66</v>
       </c>
@@ -14419,7 +14420,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="145" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>66</v>
       </c>
@@ -14511,7 +14512,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="146" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>66</v>
       </c>
@@ -14603,7 +14604,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="147" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>66</v>
       </c>
@@ -14695,7 +14696,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="148" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>66</v>
       </c>
@@ -14787,7 +14788,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="149" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>66</v>
       </c>
@@ -14879,7 +14880,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="150" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>66</v>
       </c>
@@ -14971,7 +14972,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="151" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>66</v>
       </c>
@@ -15063,7 +15064,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="152" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>66</v>
       </c>
@@ -15155,7 +15156,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="153" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>66</v>
       </c>
@@ -15247,7 +15248,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="154" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>66</v>
       </c>
@@ -15339,7 +15340,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="155" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>66</v>
       </c>
@@ -15431,7 +15432,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="156" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>66</v>
       </c>
@@ -15523,7 +15524,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="157" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>66</v>
       </c>
@@ -15615,7 +15616,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="158" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>66</v>
       </c>
@@ -15707,7 +15708,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="159" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>66</v>
       </c>
@@ -15799,7 +15800,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="160" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>66</v>
       </c>
@@ -15891,7 +15892,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="161" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>66</v>
       </c>
@@ -15983,7 +15984,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="162" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>66</v>
       </c>
@@ -16075,7 +16076,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="163" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>66</v>
       </c>
@@ -16167,7 +16168,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="164" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>66</v>
       </c>
@@ -16259,7 +16260,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="165" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>66</v>
       </c>
@@ -16351,7 +16352,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="166" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>66</v>
       </c>
@@ -16443,7 +16444,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="167" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>66</v>
       </c>
@@ -16535,7 +16536,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="168" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>66</v>
       </c>
@@ -16627,7 +16628,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="169" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>66</v>
       </c>
@@ -16719,7 +16720,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="170" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>66</v>
       </c>
@@ -16811,7 +16812,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="171" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>66</v>
       </c>
@@ -16903,7 +16904,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="172" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>66</v>
       </c>
@@ -16995,7 +16996,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="173" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>66</v>
       </c>
@@ -17087,7 +17088,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="174" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>66</v>
       </c>
@@ -17179,7 +17180,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="175" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>66</v>
       </c>
@@ -17271,7 +17272,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="176" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>66</v>
       </c>
@@ -17363,7 +17364,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="177" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>66</v>
       </c>
@@ -17455,7 +17456,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="178" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>66</v>
       </c>
@@ -17547,7 +17548,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="179" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>66</v>
       </c>
@@ -17639,7 +17640,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="180" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>66</v>
       </c>
@@ -17731,7 +17732,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="181" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>66</v>
       </c>
@@ -17823,7 +17824,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="182" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>66</v>
       </c>
@@ -17915,7 +17916,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="183" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>66</v>
       </c>
@@ -18007,7 +18008,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="184" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>66</v>
       </c>
@@ -18099,7 +18100,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="185" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>66</v>
       </c>
@@ -18191,7 +18192,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="186" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>66</v>
       </c>
@@ -18283,7 +18284,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="187" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>66</v>
       </c>
@@ -18375,7 +18376,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="188" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>66</v>
       </c>
@@ -18467,7 +18468,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="189" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>66</v>
       </c>
@@ -18559,7 +18560,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="190" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>66</v>
       </c>
@@ -18651,7 +18652,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="191" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>66</v>
       </c>
@@ -18743,7 +18744,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="192" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>66</v>
       </c>
@@ -18835,7 +18836,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="193" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>66</v>
       </c>
@@ -18927,7 +18928,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="194" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>66</v>
       </c>
@@ -19019,7 +19020,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="195" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>66</v>
       </c>
@@ -19111,7 +19112,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="196" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>66</v>
       </c>
@@ -19203,7 +19204,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="197" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>66</v>
       </c>
@@ -19295,7 +19296,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="198" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>66</v>
       </c>
@@ -19357,7 +19358,7 @@
         <v>163.16980748743401</v>
       </c>
       <c r="U198" s="3">
-        <f>R198/12.049</f>
+        <f t="shared" ref="U198:U245" si="0">R198/12.049</f>
         <v>6.7710490679412487</v>
       </c>
       <c r="V198" s="3">
@@ -19369,7 +19370,7 @@
         <v>2.1282568184633817E-5</v>
       </c>
       <c r="X198" s="3">
-        <f>S198/12.049</f>
+        <f t="shared" ref="X198:X245" si="1">S198/12.049</f>
         <v>0</v>
       </c>
       <c r="Y198" s="3">
@@ -19381,7 +19382,7 @@
         <v>0</v>
       </c>
       <c r="AA198" s="3">
-        <f>T198/12.049</f>
+        <f t="shared" ref="AA198:AA245" si="2">T198/12.049</f>
         <v>13.542186694948462</v>
       </c>
       <c r="AB198" s="3">
@@ -19396,7 +19397,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="199" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>66</v>
       </c>
@@ -19458,11 +19459,11 @@
         <v>163.16980748743401</v>
       </c>
       <c r="U199" s="3">
-        <f>R199/12.049</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V199" s="3">
-        <f t="shared" ref="V199:V209" si="0">U199/(318.15*1000)</f>
+        <f t="shared" ref="V199:V209" si="3">U199/(318.15*1000)</f>
         <v>0</v>
       </c>
       <c r="W199" s="5">
@@ -19470,11 +19471,11 @@
         <v>2.1282568184633817E-5</v>
       </c>
       <c r="X199" s="3">
-        <f>S199/12.049</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Y199" s="3">
-        <f t="shared" ref="Y199:Y209" si="1">X199/(318.15*1000)</f>
+        <f t="shared" ref="Y199:Y209" si="4">X199/(318.15*1000)</f>
         <v>0</v>
       </c>
       <c r="Z199" s="5">
@@ -19482,11 +19483,11 @@
         <v>0</v>
       </c>
       <c r="AA199" s="3">
-        <f>T199/12.049</f>
+        <f t="shared" si="2"/>
         <v>13.542186694948462</v>
       </c>
       <c r="AB199" s="3">
-        <f t="shared" ref="AB199:AB209" si="2">AA199/(318.15*1000)</f>
+        <f t="shared" ref="AB199:AB209" si="5">AA199/(318.15*1000)</f>
         <v>4.2565414725596296E-5</v>
       </c>
       <c r="AC199" s="5">
@@ -19497,7 +19498,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="200" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>66</v>
       </c>
@@ -19559,11 +19560,11 @@
         <v>233.09987741750399</v>
       </c>
       <c r="U200" s="3">
-        <f>R200/12.049</f>
+        <f t="shared" si="0"/>
         <v>10.640283220383351</v>
       </c>
       <c r="V200" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3.3444234544659282E-5</v>
       </c>
       <c r="W200" s="5">
@@ -19571,11 +19572,11 @@
         <v>5.4726802729293102E-5</v>
       </c>
       <c r="X200" s="3">
-        <f>S200/12.049</f>
+        <f t="shared" si="1"/>
         <v>3.8691455933761394</v>
       </c>
       <c r="Y200" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1.2161388003696808E-5</v>
       </c>
       <c r="Z200" s="5">
@@ -19583,11 +19584,11 @@
         <v>1.2161388003696808E-5</v>
       </c>
       <c r="AA200" s="3">
-        <f>T200/12.049</f>
+        <f t="shared" si="2"/>
         <v>19.345993644078678</v>
       </c>
       <c r="AB200" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6.080777508747031E-5</v>
       </c>
       <c r="AC200" s="5">
@@ -19598,7 +19599,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="201" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>66</v>
       </c>
@@ -19660,11 +19661,11 @@
         <v>2400.93204524967</v>
       </c>
       <c r="U201" s="3">
-        <f>R201/12.049</f>
+        <f t="shared" si="0"/>
         <v>182.81991889760147</v>
       </c>
       <c r="V201" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>5.7463435139903018E-4</v>
       </c>
       <c r="W201" s="5">
@@ -19672,11 +19673,11 @@
         <v>6.2936115412832332E-4</v>
       </c>
       <c r="X201" s="3">
-        <f>S201/12.049</f>
+        <f t="shared" si="1"/>
         <v>166.37578444855507</v>
       </c>
       <c r="Y201" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>5.2294761731433307E-4</v>
       </c>
       <c r="Z201" s="5">
@@ -19684,11 +19685,11 @@
         <v>5.3510900531802985E-4</v>
       </c>
       <c r="AA201" s="3">
-        <f>T201/12.049</f>
+        <f t="shared" si="2"/>
         <v>199.26400906711513</v>
       </c>
       <c r="AB201" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6.2632094630556384E-4</v>
       </c>
       <c r="AC201" s="5">
@@ -19699,7 +19700,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="202" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>66</v>
       </c>
@@ -19761,11 +19762,11 @@
         <v>244.75524475524401</v>
       </c>
       <c r="U202" s="3">
-        <f>R202/12.049</f>
+        <f t="shared" si="0"/>
         <v>11.607613898260352</v>
       </c>
       <c r="V202" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3.6484720723747764E-5</v>
       </c>
       <c r="W202" s="5">
@@ -19773,11 +19774,11 @@
         <v>6.6584587485207108E-4</v>
       </c>
       <c r="X202" s="3">
-        <f>S202/12.049</f>
+        <f t="shared" si="1"/>
         <v>4.8364762712531748</v>
       </c>
       <c r="Y202" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1.52018741827854E-5</v>
       </c>
       <c r="Z202" s="5">
@@ -19785,11 +19786,11 @@
         <v>5.503108795008152E-4</v>
       </c>
       <c r="AA202" s="3">
-        <f>T202/12.049</f>
+        <f t="shared" si="2"/>
         <v>20.313324321955683</v>
       </c>
       <c r="AB202" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6.3848261266558805E-5</v>
       </c>
       <c r="AC202" s="5">
@@ -19800,7 +19801,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="203" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>66</v>
       </c>
@@ -19862,11 +19863,11 @@
         <v>174.825174825174</v>
       </c>
       <c r="U203" s="3">
-        <f>R203/12.049</f>
+        <f t="shared" si="0"/>
         <v>1.9345727966880653</v>
       </c>
       <c r="V203" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.0806940018483897E-6</v>
       </c>
       <c r="W203" s="5">
@@ -19874,11 +19875,11 @@
         <v>6.7192656885391947E-4</v>
       </c>
       <c r="X203" s="3">
-        <f>S203/12.049</f>
+        <f t="shared" si="1"/>
         <v>1.9345727966880653</v>
       </c>
       <c r="Y203" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>6.0806940018483897E-6</v>
       </c>
       <c r="Z203" s="5">
@@ -19886,11 +19887,11 @@
         <v>5.5639157350266359E-4</v>
       </c>
       <c r="AA203" s="3">
-        <f>T203/12.049</f>
+        <f t="shared" si="2"/>
         <v>14.509517372825464</v>
       </c>
       <c r="AB203" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>4.5605900904684784E-5</v>
       </c>
       <c r="AC203" s="5">
@@ -19901,7 +19902,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="204" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>66</v>
       </c>
@@ -19963,11 +19964,11 @@
         <v>442.89008720771398</v>
       </c>
       <c r="U204" s="3">
-        <f>R204/12.049</f>
+        <f t="shared" si="0"/>
         <v>20.799236451157775</v>
       </c>
       <c r="V204" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.5375566403136175E-5</v>
       </c>
       <c r="W204" s="5">
@@ -19975,11 +19976,11 @@
         <v>6.5375566403136175E-5</v>
       </c>
       <c r="X204" s="3">
-        <f>S204/12.049</f>
+        <f t="shared" si="1"/>
         <v>5.8038069491302107</v>
       </c>
       <c r="Y204" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1.8242360361873994E-5</v>
       </c>
       <c r="Z204" s="5">
@@ -19987,11 +19988,11 @@
         <v>1.8242360361873994E-5</v>
       </c>
       <c r="AA204" s="3">
-        <f>T204/12.049</f>
+        <f t="shared" si="2"/>
         <v>36.757414491469333</v>
       </c>
       <c r="AB204" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1.1553485617309235E-4</v>
       </c>
       <c r="AC204" s="5">
@@ -20002,7 +20003,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="205" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>66</v>
       </c>
@@ -20064,11 +20065,11 @@
         <v>349.65034965034903</v>
       </c>
       <c r="U205" s="3">
-        <f>R205/12.049</f>
+        <f t="shared" si="0"/>
         <v>15.424516557390655</v>
       </c>
       <c r="V205" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>4.8481900227536239E-5</v>
       </c>
       <c r="W205" s="5">
@@ -20076,11 +20077,11 @@
         <v>1.1385746663067242E-4</v>
       </c>
       <c r="X205" s="3">
-        <f>S205/12.049</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Y205" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Z205" s="5">
@@ -20088,11 +20089,11 @@
         <v>1.8242360361873994E-5</v>
       </c>
       <c r="AA205" s="3">
-        <f>T205/12.049</f>
+        <f t="shared" si="2"/>
         <v>29.019034745651012</v>
       </c>
       <c r="AB205" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>9.121180180936984E-5</v>
       </c>
       <c r="AC205" s="5">
@@ -20103,7 +20104,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="206" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>66</v>
       </c>
@@ -20165,11 +20166,11 @@
         <v>2307.6923076922999</v>
       </c>
       <c r="U206" s="3">
-        <f>R206/12.049</f>
+        <f t="shared" si="0"/>
         <v>158.02971200929537</v>
       </c>
       <c r="V206" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>4.967144806201332E-4</v>
       </c>
       <c r="W206" s="5">
@@ -20177,11 +20178,11 @@
         <v>6.1057194725080565E-4</v>
       </c>
       <c r="X206" s="3">
-        <f>S206/12.049</f>
+        <f t="shared" si="1"/>
         <v>120.91261525385676</v>
       </c>
       <c r="Y206" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>3.8004908142026325E-4</v>
       </c>
       <c r="Z206" s="5">
@@ -20189,11 +20190,11 @@
         <v>3.9829144178213724E-4</v>
       </c>
       <c r="AA206" s="3">
-        <f>T206/12.049</f>
+        <f t="shared" si="2"/>
         <v>191.52562932129638</v>
       </c>
       <c r="AB206" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6.0199789194184E-4</v>
       </c>
       <c r="AC206" s="5">
@@ -20204,7 +20205,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="207" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>66</v>
       </c>
@@ -20266,11 +20267,11 @@
         <v>3333.33315549196</v>
       </c>
       <c r="U207" s="3">
-        <f>R207/12.049</f>
+        <f t="shared" si="0"/>
         <v>224.4310731181011</v>
       </c>
       <c r="V207" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.0542534376269396E-4</v>
       </c>
       <c r="W207" s="5">
@@ -20278,11 +20279,11 @@
         <v>1.3159972910134995E-3</v>
       </c>
       <c r="X207" s="3">
-        <f>S207/12.049</f>
+        <f t="shared" si="1"/>
         <v>167.34307084689851</v>
       </c>
       <c r="Y207" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>5.2598796431525547E-4</v>
       </c>
       <c r="Z207" s="5">
@@ -20290,11 +20291,11 @@
         <v>9.2427940609739277E-4</v>
       </c>
       <c r="AA207" s="3">
-        <f>T207/12.049</f>
+        <f t="shared" si="2"/>
         <v>276.6481164820284</v>
       </c>
       <c r="AB207" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>8.6955246418993681E-4</v>
       </c>
       <c r="AC207" s="5">
@@ -20305,7 +20306,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="208" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>66</v>
       </c>
@@ -20367,11 +20368,11 @@
         <v>2132.8671328671298</v>
       </c>
       <c r="U208" s="3">
-        <f>R208/12.049</f>
+        <f t="shared" si="0"/>
         <v>129.25553987882813</v>
       </c>
       <c r="V208" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>4.0627232399443073E-4</v>
       </c>
       <c r="W208" s="5">
@@ -20379,11 +20380,11 @@
         <v>1.7222696150079302E-3</v>
       </c>
       <c r="X208" s="3">
-        <f>S208/12.049</f>
+        <f t="shared" si="1"/>
         <v>77.384063135380785</v>
       </c>
       <c r="Y208" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>2.4323137870621022E-4</v>
       </c>
       <c r="Z208" s="5">
@@ -20391,11 +20392,11 @@
         <v>1.167510784803603E-3</v>
       </c>
       <c r="AA208" s="3">
-        <f>T208/12.049</f>
+        <f t="shared" si="2"/>
         <v>177.01611194847123</v>
       </c>
       <c r="AB208" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>5.5639199103715614E-4</v>
       </c>
       <c r="AC208" s="5">
@@ -20406,7 +20407,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="209" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>66</v>
       </c>
@@ -20468,11 +20469,11 @@
         <v>466.19975483500798</v>
       </c>
       <c r="U209" s="3">
-        <f>R209/12.049</f>
+        <f t="shared" si="0"/>
         <v>31.866544941488918</v>
       </c>
       <c r="V209" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.0016201458899551E-4</v>
       </c>
       <c r="W209" s="5">
@@ -20480,11 +20481,11 @@
         <v>1.8224316295969258E-3</v>
       </c>
       <c r="X209" s="3">
-        <f>S209/12.049</f>
+        <f t="shared" si="1"/>
         <v>11.607613898260352</v>
       </c>
       <c r="Y209" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>3.6484720723747764E-5</v>
       </c>
       <c r="Z209" s="5">
@@ -20492,11 +20493,11 @@
         <v>1.2039955055273509E-3</v>
       </c>
       <c r="AA209" s="3">
-        <f>T209/12.049</f>
+        <f t="shared" si="2"/>
         <v>38.691987288157357</v>
       </c>
       <c r="AB209" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1.2161555017494062E-4</v>
       </c>
       <c r="AC209" s="5">
@@ -20507,7 +20508,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="210" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>66</v>
       </c>
@@ -20569,7 +20570,7 @@
         <v>1287.7361882237699</v>
       </c>
       <c r="U210" s="3">
-        <f>R210/12.049</f>
+        <f t="shared" si="0"/>
         <v>95.27761639970123</v>
       </c>
       <c r="V210" s="3">
@@ -20581,7 +20582,7 @@
         <v>1.9279941802521599E-4</v>
       </c>
       <c r="X210" s="3">
-        <f>S210/12.049</f>
+        <f t="shared" si="1"/>
         <v>83.385880734057608</v>
       </c>
       <c r="Y210" s="3">
@@ -20593,7 +20594,7 @@
         <v>1.6873584672398237E-4</v>
       </c>
       <c r="AA210" s="3">
-        <f>T210/12.049</f>
+        <f t="shared" si="2"/>
         <v>106.87494300139181</v>
       </c>
       <c r="AB210" s="3">
@@ -20608,7 +20609,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="211" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>66</v>
       </c>
@@ -20670,11 +20671,11 @@
         <v>679.24523412990595</v>
       </c>
       <c r="U211" s="3">
-        <f>R211/12.049</f>
+        <f t="shared" si="0"/>
         <v>35.734085816250314</v>
       </c>
       <c r="V211" s="3">
-        <f t="shared" ref="V211:V221" si="3">U211/(494.18*1000)</f>
+        <f t="shared" ref="V211:V221" si="6">U211/(494.18*1000)</f>
         <v>7.2309858384091456E-5</v>
       </c>
       <c r="W211" s="5">
@@ -20682,11 +20683,11 @@
         <v>2.6510927640930747E-4</v>
       </c>
       <c r="X211" s="3">
-        <f>S211/12.049</f>
+        <f t="shared" si="1"/>
         <v>30.535651918655159</v>
       </c>
       <c r="Y211" s="3">
-        <f t="shared" ref="Y211:Y221" si="4">X211/(494.18*1000)</f>
+        <f t="shared" ref="Y211:Y221" si="7">X211/(494.18*1000)</f>
         <v>6.1790545790309516E-5</v>
       </c>
       <c r="Z211" s="5">
@@ -20694,11 +20695,11 @@
         <v>2.305263925142919E-4</v>
       </c>
       <c r="AA211" s="3">
-        <f>T211/12.049</f>
+        <f t="shared" si="2"/>
         <v>56.373577403096192</v>
       </c>
       <c r="AB211" s="3">
-        <f t="shared" ref="AB211:AB221" si="5">AA211/(494.18*1000)</f>
+        <f t="shared" ref="AB211:AB221" si="8">AA211/(494.18*1000)</f>
         <v>1.1407498766258487E-4</v>
       </c>
       <c r="AC211" s="5">
@@ -20709,7 +20710,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="212" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>66</v>
       </c>
@@ -20771,11 +20772,11 @@
         <v>2504.7168008540302</v>
       </c>
       <c r="U212" s="3">
-        <f>R212/12.049</f>
+        <f t="shared" si="0"/>
         <v>197.35247738401529</v>
       </c>
       <c r="V212" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3.9935342867784064E-4</v>
       </c>
       <c r="W212" s="5">
@@ -20783,11 +20784,11 @@
         <v>6.6446270508714817E-4</v>
       </c>
       <c r="X212" s="3">
-        <f>S212/12.049</f>
+        <f t="shared" si="1"/>
         <v>184.38861193064903</v>
       </c>
       <c r="Y212" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>3.7312034467329523E-4</v>
       </c>
       <c r="Z212" s="5">
@@ -20795,11 +20796,11 @@
         <v>6.0364673718758712E-4</v>
       </c>
       <c r="AA212" s="3">
-        <f>T212/12.049</f>
+        <f t="shared" si="2"/>
         <v>207.87756667391736</v>
       </c>
       <c r="AB212" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>4.2065151700578201E-4</v>
       </c>
       <c r="AC212" s="5">
@@ -20810,7 +20811,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="213" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>66</v>
       </c>
@@ -20872,11 +20873,11 @@
         <v>5094.3392559742997</v>
       </c>
       <c r="U213" s="3">
-        <f>R213/12.049</f>
+        <f t="shared" si="0"/>
         <v>409.18084488339287</v>
       </c>
       <c r="V213" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>8.2799960517097588E-4</v>
       </c>
       <c r="W213" s="5">
@@ -20884,11 +20885,11 @@
         <v>1.4924623102581241E-3</v>
       </c>
       <c r="X213" s="3">
-        <f>S213/12.049</f>
+        <f t="shared" si="1"/>
         <v>387.56834464628685</v>
       </c>
       <c r="Y213" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>7.8426554018027207E-4</v>
       </c>
       <c r="Z213" s="5">
@@ -20896,11 +20897,11 @@
         <v>1.3879122773678592E-3</v>
       </c>
       <c r="AA213" s="3">
-        <f>T213/12.049</f>
+        <f t="shared" si="2"/>
         <v>422.80183052322184</v>
       </c>
       <c r="AB213" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>8.5556240746938737E-4</v>
       </c>
       <c r="AC213" s="5">
@@ -20911,7 +20912,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="214" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>66</v>
       </c>
@@ -20973,11 +20974,11 @@
         <v>707.54668703283005</v>
       </c>
       <c r="U214" s="3">
-        <f>R214/12.049</f>
+        <f t="shared" si="0"/>
         <v>45.388828948460457</v>
       </c>
       <c r="V214" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>9.1846754114817387E-5</v>
       </c>
       <c r="W214" s="5">
@@ -20985,11 +20986,11 @@
         <v>1.5843090643729413E-3</v>
       </c>
       <c r="X214" s="3">
-        <f>S214/12.049</f>
+        <f t="shared" si="1"/>
         <v>37.58234909404225</v>
       </c>
       <c r="Y214" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>7.6049919248132763E-5</v>
       </c>
       <c r="Z214" s="5">
@@ -20997,11 +20998,11 @@
         <v>1.463962196615992E-3</v>
       </c>
       <c r="AA214" s="3">
-        <f>T214/12.049</f>
+        <f t="shared" si="2"/>
         <v>58.722440620203344</v>
       </c>
       <c r="AB214" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1.1882803962160214E-4</v>
       </c>
       <c r="AC214" s="5">
@@ -21012,7 +21013,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="215" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>66</v>
       </c>
@@ -21074,11 +21075,11 @@
         <v>353.77399129514902</v>
       </c>
       <c r="U215" s="3">
-        <f>R215/12.049</f>
+        <f t="shared" si="0"/>
         <v>6.0976014607021334</v>
       </c>
       <c r="V215" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1.2338826866125973E-5</v>
       </c>
       <c r="W215" s="5">
@@ -21086,11 +21087,11 @@
         <v>1.5966478912390672E-3</v>
       </c>
       <c r="X215" s="3">
-        <f>S215/12.049</f>
+        <f t="shared" si="1"/>
         <v>5.8722118048005978</v>
       </c>
       <c r="Y215" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1.1882738687928685E-5</v>
       </c>
       <c r="Z215" s="5">
@@ -21098,11 +21099,11 @@
         <v>1.4758449353039207E-3</v>
       </c>
       <c r="AA215" s="3">
-        <f>T215/12.049</f>
+        <f t="shared" si="2"/>
         <v>29.361274072134538</v>
       </c>
       <c r="AB215" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>5.9414128601186894E-5</v>
       </c>
       <c r="AC215" s="5">
@@ -21113,7 +21114,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="216" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>66</v>
       </c>
@@ -21175,11 +21176,11 @@
         <v>4845.6056588725396</v>
       </c>
       <c r="U216" s="3">
-        <f>R216/12.049</f>
+        <f t="shared" si="0"/>
         <v>338.24715744045147</v>
       </c>
       <c r="V216" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>6.8446144611366601E-4</v>
       </c>
       <c r="W216" s="5">
@@ -21187,11 +21188,11 @@
         <v>6.8446144611366601E-4</v>
       </c>
       <c r="X216" s="3">
-        <f>S216/12.049</f>
+        <f t="shared" si="1"/>
         <v>275.59671081087396</v>
       </c>
       <c r="Y216" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>5.5768487354986842E-4</v>
       </c>
       <c r="Z216" s="5">
@@ -21199,11 +21200,11 @@
         <v>5.5768487354986842E-4</v>
       </c>
       <c r="AA216" s="3">
-        <f>T216/12.049</f>
+        <f t="shared" si="2"/>
         <v>402.15832507864053</v>
       </c>
       <c r="AB216" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>8.1378915593233344E-4</v>
       </c>
       <c r="AC216" s="5">
@@ -21214,7 +21215,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="217" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>66</v>
       </c>
@@ -21276,11 +21277,11 @@
         <v>1510.6880209984099</v>
       </c>
       <c r="U217" s="3">
-        <f>R217/12.049</f>
+        <f t="shared" si="0"/>
         <v>98.261266495144838</v>
       </c>
       <c r="V217" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1.988369956192983E-4</v>
       </c>
       <c r="W217" s="5">
@@ -21288,11 +21289,11 @@
         <v>8.8329844173296425E-4</v>
       </c>
       <c r="X217" s="3">
-        <f>S217/12.049</f>
+        <f t="shared" si="1"/>
         <v>54.409585994251891</v>
       </c>
       <c r="Y217" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1.1010074465630315E-4</v>
       </c>
       <c r="Z217" s="5">
@@ -21300,11 +21301,11 @@
         <v>6.6778561820617153E-4</v>
       </c>
       <c r="AA217" s="3">
-        <f>T217/12.049</f>
+        <f t="shared" si="2"/>
         <v>125.37870536960827</v>
       </c>
       <c r="AB217" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>2.5371060214822184E-4</v>
       </c>
       <c r="AC217" s="5">
@@ -21315,7 +21316,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="218" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>66</v>
       </c>
@@ -21377,11 +21378,11 @@
         <v>5159.1446451706197</v>
       </c>
       <c r="U218" s="3">
-        <f>R218/12.049</f>
+        <f t="shared" si="0"/>
         <v>335.94572163665038</v>
       </c>
       <c r="V218" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>6.7980436609464234E-4</v>
       </c>
       <c r="W218" s="5">
@@ -21389,11 +21390,11 @@
         <v>1.5631028078276067E-3</v>
       </c>
       <c r="X218" s="3">
-        <f>S218/12.049</f>
+        <f t="shared" si="1"/>
         <v>243.66060709196367</v>
       </c>
       <c r="Y218" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>4.9306043767850512E-4</v>
       </c>
       <c r="Z218" s="5">
@@ -21401,11 +21402,11 @@
         <v>1.1608460558846768E-3</v>
       </c>
       <c r="AA218" s="3">
-        <f>T218/12.049</f>
+        <f t="shared" si="2"/>
         <v>428.18031746789109</v>
       </c>
       <c r="AB218" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>8.6644606715749538E-4</v>
       </c>
       <c r="AC218" s="5">
@@ -21416,7 +21417,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="219" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>66</v>
       </c>
@@ -21478,11 +21479,11 @@
         <v>6000</v>
       </c>
       <c r="U219" s="3">
-        <f>R219/12.049</f>
+        <f t="shared" si="0"/>
         <v>444.71574404514899</v>
       </c>
       <c r="V219" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>8.9990639856964865E-4</v>
       </c>
       <c r="W219" s="5">
@@ -21490,11 +21491,11 @@
         <v>2.4630092063972556E-3</v>
       </c>
       <c r="X219" s="3">
-        <f>S219/12.049</f>
+        <f t="shared" si="1"/>
         <v>391.51295717233717</v>
       </c>
       <c r="Y219" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>7.9224767730854578E-4</v>
       </c>
       <c r="Z219" s="5">
@@ -21502,11 +21503,11 @@
         <v>1.9530937331932226E-3</v>
       </c>
       <c r="AA219" s="3">
-        <f>T219/12.049</f>
+        <f t="shared" si="2"/>
         <v>497.96663623537228</v>
       </c>
       <c r="AB219" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1.0076624635464249E-3</v>
       </c>
       <c r="AC219" s="5">
@@ -21517,7 +21518,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="220" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>66</v>
       </c>
@@ -21579,11 +21580,11 @@
         <v>1895.48613470756</v>
       </c>
       <c r="U220" s="3">
-        <f>R220/12.049</f>
+        <f t="shared" si="0"/>
         <v>146.02788613162917</v>
       </c>
       <c r="V220" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>2.9549533799754982E-4</v>
       </c>
       <c r="W220" s="5">
@@ -21591,11 +21592,11 @@
         <v>2.7585045443948054E-3</v>
       </c>
       <c r="X220" s="3">
-        <f>S220/12.049</f>
+        <f t="shared" si="1"/>
         <v>118.28179343207236</v>
       </c>
       <c r="Y220" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>2.3934961639902942E-4</v>
       </c>
       <c r="Z220" s="5">
@@ -21603,11 +21604,11 @@
         <v>2.1924433495922519E-3</v>
       </c>
       <c r="AA220" s="3">
-        <f>T220/12.049</f>
+        <f t="shared" si="2"/>
         <v>157.31480908851856</v>
       </c>
       <c r="AB220" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3.1833503801958509E-4</v>
       </c>
       <c r="AC220" s="5">
@@ -21618,7 +21619,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="221" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>66</v>
       </c>
@@ -21680,11 +21681,11 @@
         <v>584.32262662847199</v>
       </c>
       <c r="U221" s="3">
-        <f>R221/12.049</f>
+        <f t="shared" si="0"/>
         <v>17.690264752261601</v>
       </c>
       <c r="V221" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3.5797209017486746E-5</v>
       </c>
       <c r="W221" s="5">
@@ -21692,11 +21693,11 @@
         <v>2.7943017534122921E-3</v>
       </c>
       <c r="X221" s="3">
-        <f>S221/12.049</f>
+        <f t="shared" si="1"/>
         <v>2.3656012157511328</v>
       </c>
       <c r="Y221" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>4.7869222059798713E-6</v>
       </c>
       <c r="Z221" s="5">
@@ -21704,11 +21705,11 @@
         <v>2.1972302717982316E-3</v>
       </c>
       <c r="AA221" s="3">
-        <f>T221/12.049</f>
+        <f t="shared" si="2"/>
         <v>48.495528809732924</v>
       </c>
       <c r="AB221" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>9.8133329575727309E-5</v>
       </c>
       <c r="AC221" s="5">
@@ -21719,7 +21720,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="222" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>66</v>
       </c>
@@ -21781,7 +21782,7 @@
         <v>13.7283445388401</v>
       </c>
       <c r="U222" s="3">
-        <f>R222/12.049</f>
+        <f t="shared" si="0"/>
         <v>0.76188895344011953</v>
       </c>
       <c r="V222" s="3">
@@ -21793,7 +21794,7 @@
         <v>2.3797131229389041E-6</v>
       </c>
       <c r="X222" s="3">
-        <f>S222/12.049</f>
+        <f t="shared" si="1"/>
         <v>0.29983903601151718</v>
       </c>
       <c r="Y222" s="3">
@@ -21805,7 +21806,7 @@
         <v>9.3652872317440393E-7</v>
       </c>
       <c r="AA222" s="3">
-        <f>T222/12.049</f>
+        <f t="shared" si="2"/>
         <v>1.1393762585144078</v>
       </c>
       <c r="AB222" s="3">
@@ -21820,7 +21821,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="223" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>66</v>
       </c>
@@ -21882,11 +21883,11 @@
         <v>7.9480202781350604</v>
       </c>
       <c r="U223" s="3">
-        <f>R223/12.049</f>
+        <f t="shared" si="0"/>
         <v>0.14109054693335546</v>
       </c>
       <c r="V223" s="3">
-        <f t="shared" ref="V223:V233" si="6">U223/(320.16*1000)</f>
+        <f t="shared" ref="V223:V233" si="9">U223/(320.16*1000)</f>
         <v>4.406876153590563E-7</v>
       </c>
       <c r="W223" s="5">
@@ -21894,11 +21895,11 @@
         <v>2.8204007382979604E-6</v>
       </c>
       <c r="X223" s="3">
-        <f>S223/12.049</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Y223" s="3">
-        <f t="shared" ref="Y223:Y233" si="7">X223/(320.16*1000)</f>
+        <f t="shared" ref="Y223:Y233" si="10">X223/(320.16*1000)</f>
         <v>0</v>
       </c>
       <c r="Z223" s="5">
@@ -21906,11 +21907,11 @@
         <v>9.3652872317440393E-7</v>
       </c>
       <c r="AA223" s="3">
-        <f>T223/12.049</f>
+        <f t="shared" si="2"/>
         <v>0.65964148710557402</v>
       </c>
       <c r="AB223" s="3">
-        <f t="shared" ref="AB223:AB233" si="8">AA223/(320.16*1000)</f>
+        <f t="shared" ref="AB223:AB233" si="11">AA223/(320.16*1000)</f>
         <v>2.0603494724686844E-6</v>
       </c>
       <c r="AC223" s="5">
@@ -21921,7 +21922,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="224" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>66</v>
       </c>
@@ -21983,11 +21984,11 @@
         <v>28.9017536051532</v>
       </c>
       <c r="U224" s="3">
-        <f>R224/12.049</f>
+        <f t="shared" si="0"/>
         <v>1.9038924392065733</v>
       </c>
       <c r="V224" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>5.9466905272569129E-6</v>
       </c>
       <c r="W224" s="5">
@@ -21995,11 +21996,11 @@
         <v>8.7670912655548729E-6</v>
       </c>
       <c r="X224" s="3">
-        <f>S224/12.049</f>
+        <f t="shared" si="1"/>
         <v>1.2593085788291976</v>
       </c>
       <c r="Y224" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>3.933372622529977E-6</v>
       </c>
       <c r="Z224" s="5">
@@ -22007,11 +22008,11 @@
         <v>4.8699013457043806E-6</v>
       </c>
       <c r="AA224" s="3">
-        <f>T224/12.049</f>
+        <f t="shared" si="2"/>
         <v>2.3986848373436138</v>
       </c>
       <c r="AB224" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>7.4921440446764548E-6</v>
       </c>
       <c r="AC224" s="5">
@@ -22022,7 +22023,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="225" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>66</v>
       </c>
@@ -22084,11 +22085,11 @@
         <v>80.202338140204205</v>
       </c>
       <c r="U225" s="3">
-        <f>R225/12.049</f>
+        <f t="shared" si="0"/>
         <v>6.1963648435554814</v>
       </c>
       <c r="V225" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1.9353963154533613E-5</v>
       </c>
       <c r="W225" s="5">
@@ -22096,11 +22097,11 @@
         <v>2.8121054420088486E-5</v>
       </c>
       <c r="X225" s="3">
-        <f>S225/12.049</f>
+        <f t="shared" si="1"/>
         <v>5.6369068971901237</v>
       </c>
       <c r="Y225" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1.7606530788324975E-5</v>
       </c>
       <c r="Z225" s="5">
@@ -22108,11 +22109,11 @@
         <v>2.2476432134029355E-5</v>
       </c>
       <c r="AA225" s="3">
-        <f>T225/12.049</f>
+        <f t="shared" si="2"/>
         <v>6.6563480903148982</v>
       </c>
       <c r="AB225" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2.079069243601605E-5</v>
       </c>
       <c r="AC225" s="5">
@@ -22123,7 +22124,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="226" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>66</v>
       </c>
@@ -22185,11 +22186,11 @@
         <v>70.086721070859895</v>
       </c>
       <c r="U226" s="3">
-        <f>R226/12.049</f>
+        <f t="shared" si="0"/>
         <v>5.4593742219271313</v>
       </c>
       <c r="V226" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1.7052018434305134E-5</v>
       </c>
       <c r="W226" s="5">
@@ -22197,11 +22198,11 @@
         <v>4.5173072854393616E-5</v>
       </c>
       <c r="X226" s="3">
-        <f>S226/12.049</f>
+        <f t="shared" si="1"/>
         <v>4.7374007694549753</v>
       </c>
       <c r="Y226" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1.4796978915089253E-5</v>
       </c>
       <c r="Z226" s="5">
@@ -22209,11 +22210,11 @@
         <v>3.7273411049118605E-5</v>
       </c>
       <c r="AA226" s="3">
-        <f>T226/12.049</f>
+        <f t="shared" si="2"/>
         <v>5.8168081227371484</v>
       </c>
       <c r="AB226" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1.8168441162972103E-5</v>
       </c>
       <c r="AC226" s="5">
@@ -22224,7 +22225,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="227" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>66</v>
       </c>
@@ -22286,11 +22287,11 @@
         <v>15.8959744054563</v>
       </c>
       <c r="U227" s="3">
-        <f>R227/12.049</f>
+        <f t="shared" si="0"/>
         <v>0.61747862893186167</v>
       </c>
       <c r="V227" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1.9286563872184584E-6</v>
       </c>
       <c r="W227" s="5">
@@ -22298,11 +22299,11 @@
         <v>4.7101729241612072E-5</v>
       </c>
       <c r="X227" s="3">
-        <f>S227/12.049</f>
+        <f t="shared" si="1"/>
         <v>0.17990122554702798</v>
       </c>
       <c r="Y227" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>5.619103746471389E-7</v>
       </c>
       <c r="Z227" s="5">
@@ -22310,11 +22311,11 @@
         <v>3.7835321423765743E-5</v>
       </c>
       <c r="AA227" s="3">
-        <f>T227/12.049</f>
+        <f t="shared" si="2"/>
         <v>1.319277484061441</v>
       </c>
       <c r="AB227" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>4.1206817967936062E-6</v>
       </c>
       <c r="AC227" s="5">
@@ -22325,7 +22326,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="228" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>66</v>
       </c>
@@ -22387,11 +22388,11 @@
         <v>59.971137076922503</v>
       </c>
       <c r="U228" s="3">
-        <f>R228/12.049</f>
+        <f t="shared" si="0"/>
         <v>3.8849697070296294</v>
       </c>
       <c r="V228" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1.2134463102916134E-5</v>
       </c>
       <c r="W228" s="5">
@@ -22399,11 +22400,11 @@
         <v>1.2134463102916134E-5</v>
       </c>
       <c r="X228" s="3">
-        <f>S228/12.049</f>
+        <f t="shared" si="1"/>
         <v>2.9383885139846959</v>
       </c>
       <c r="Y228" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>9.1778751686178652E-6</v>
       </c>
       <c r="Z228" s="5">
@@ -22411,11 +22412,11 @@
         <v>9.1778751686178652E-6</v>
       </c>
       <c r="AA228" s="3">
-        <f>T228/12.049</f>
+        <f t="shared" si="2"/>
         <v>4.9772709002342523</v>
       </c>
       <c r="AB228" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1.5546198464000039E-5</v>
       </c>
       <c r="AC228" s="5">
@@ -22426,7 +22427,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="229" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>66</v>
       </c>
@@ -22488,11 +22489,11 @@
         <v>31.069383471769299</v>
       </c>
       <c r="U229" s="3">
-        <f>R229/12.049</f>
+        <f t="shared" si="0"/>
         <v>1.8474562204332312</v>
       </c>
       <c r="V229" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>5.7704154811132911E-6</v>
       </c>
       <c r="W229" s="5">
@@ -22500,11 +22501,11 @@
         <v>1.7904878584029426E-5</v>
       </c>
       <c r="X229" s="3">
-        <f>S229/12.049</f>
+        <f t="shared" si="1"/>
         <v>1.0194439381996265</v>
       </c>
       <c r="Y229" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>3.1841702217629516E-6</v>
       </c>
       <c r="Z229" s="5">
@@ -22512,11 +22513,11 @@
         <v>1.2362045390380817E-5</v>
       </c>
       <c r="AA229" s="3">
-        <f>T229/12.049</f>
+        <f t="shared" si="2"/>
         <v>2.5785860628906381</v>
       </c>
       <c r="AB229" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>8.0540544193235814E-6</v>
       </c>
       <c r="AC229" s="5">
@@ -22527,7 +22528,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="230" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>66</v>
       </c>
@@ -22589,11 +22590,11 @@
         <v>158.95954560212101</v>
       </c>
       <c r="U230" s="3">
-        <f>R230/12.049</f>
+        <f t="shared" si="0"/>
         <v>9.3609428168312725</v>
       </c>
       <c r="V230" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2.9238327139028212E-5</v>
       </c>
       <c r="W230" s="5">
@@ -22601,11 +22602,11 @@
         <v>4.7143205723057641E-5</v>
       </c>
       <c r="X230" s="3">
-        <f>S230/12.049</f>
+        <f t="shared" si="1"/>
         <v>5.3970395114857004</v>
       </c>
       <c r="Y230" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1.6857319813486069E-5</v>
       </c>
       <c r="Z230" s="5">
@@ -22613,11 +22614,11 @@
         <v>2.9219365203866886E-5</v>
       </c>
       <c r="AA230" s="3">
-        <f>T230/12.049</f>
+        <f t="shared" si="2"/>
         <v>13.192758370165244</v>
       </c>
       <c r="AB230" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>4.1206766523504634E-5</v>
       </c>
       <c r="AC230" s="5">
@@ -22628,7 +22629,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="231" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>66</v>
       </c>
@@ -22690,11 +22691,11 @@
         <v>214.595389870405</v>
       </c>
       <c r="U231" s="3">
-        <f>R231/12.049</f>
+        <f t="shared" si="0"/>
         <v>15.805461034110715</v>
       </c>
       <c r="V231" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>4.9367382040575699E-5</v>
       </c>
       <c r="W231" s="5">
@@ -22702,11 +22703,11 @@
         <v>9.6510587763633346E-5</v>
       </c>
       <c r="X231" s="3">
-        <f>S231/12.049</f>
+        <f t="shared" si="1"/>
         <v>13.492594661101917</v>
       </c>
       <c r="Y231" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>4.2143286672607188E-5</v>
       </c>
       <c r="Z231" s="5">
@@ -22714,11 +22715,11 @@
         <v>7.1362651876474077E-5</v>
       </c>
       <c r="AA231" s="3">
-        <f>T231/12.049</f>
+        <f t="shared" si="2"/>
         <v>17.810224074230643</v>
       </c>
       <c r="AB231" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>5.5629135664138688E-5</v>
       </c>
       <c r="AC231" s="5">
@@ -22729,7 +22730,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="232" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>66</v>
       </c>
@@ -22791,11 +22792,11 @@
         <v>96.098279470253601</v>
       </c>
       <c r="U232" s="3">
-        <f>R232/12.049</f>
+        <f t="shared" si="0"/>
         <v>5.677649597476969</v>
       </c>
       <c r="V232" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1.7733788098066493E-5</v>
       </c>
       <c r="W232" s="5">
@@ -22803,11 +22804,11 @@
         <v>1.1424437586169984E-4</v>
       </c>
       <c r="X232" s="3">
-        <f>S232/12.049</f>
+        <f t="shared" si="1"/>
         <v>3.5380610958580219</v>
       </c>
       <c r="Y232" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1.1050915466822907E-5</v>
       </c>
       <c r="Z232" s="5">
@@ -22815,11 +22816,11 @@
         <v>8.2413567343296988E-5</v>
       </c>
       <c r="AA232" s="3">
-        <f>T232/12.049</f>
+        <f t="shared" si="2"/>
         <v>7.9756228293014857</v>
       </c>
       <c r="AB232" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2.4911365658737775E-5</v>
       </c>
       <c r="AC232" s="5">
@@ -22830,7 +22831,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="233" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>66</v>
       </c>
@@ -22892,11 +22893,11 @@
         <v>52.7456821379307</v>
       </c>
       <c r="U233" s="3">
-        <f>R233/12.049</f>
+        <f t="shared" si="0"/>
         <v>2.5894265084239358</v>
       </c>
       <c r="V233" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>8.0879138818838568E-6</v>
       </c>
       <c r="W233" s="5">
@@ -22904,11 +22905,11 @@
         <v>1.2233228974358368E-4</v>
       </c>
       <c r="X233" s="3">
-        <f>S233/12.049</f>
+        <f t="shared" si="1"/>
         <v>1.7390488403877418</v>
       </c>
       <c r="Y233" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>5.4318117203515174E-6</v>
       </c>
       <c r="Z233" s="5">
@@ -22916,11 +22917,11 @@
         <v>8.7845379063648509E-5</v>
       </c>
       <c r="AA233" s="3">
-        <f>T233/12.049</f>
+        <f t="shared" si="2"/>
         <v>4.377598318360918</v>
       </c>
       <c r="AB233" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1.3673158165794971E-5</v>
       </c>
       <c r="AC233" s="5">
@@ -22931,7 +22932,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="234" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>66</v>
       </c>
@@ -22993,7 +22994,7 @@
         <v>174.27815114419201</v>
       </c>
       <c r="U234" s="3">
-        <f>R234/12.049</f>
+        <f t="shared" si="0"/>
         <v>8.1027471159432309</v>
       </c>
       <c r="V234" s="3">
@@ -23005,7 +23006,7 @@
         <v>1.6329895374852083E-5</v>
       </c>
       <c r="X234" s="3">
-        <f>S234/12.049</f>
+        <f t="shared" si="1"/>
         <v>3.3110695661269567</v>
       </c>
       <c r="Y234" s="3">
@@ -23017,7 +23018,7 @@
         <v>6.672973847020516E-6</v>
       </c>
       <c r="AA234" s="3">
-        <f>T234/12.049</f>
+        <f t="shared" si="2"/>
         <v>14.464117449098847</v>
       </c>
       <c r="AB234" s="3">
@@ -23032,7 +23033,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="235" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>66</v>
       </c>
@@ -23094,11 +23095,11 @@
         <v>48.32</v>
       </c>
       <c r="U235" s="3">
-        <f>R235/12.049</f>
+        <f t="shared" si="0"/>
         <v>4.0102913104821978</v>
       </c>
       <c r="V235" s="3">
-        <f t="shared" ref="V235:V245" si="9">U235/(496.191*1000)</f>
+        <f t="shared" ref="V235:V245" si="12">U235/(496.191*1000)</f>
         <v>8.0821524583924291E-6</v>
       </c>
       <c r="W235" s="5">
@@ -23106,11 +23107,11 @@
         <v>2.4412047833244513E-5</v>
       </c>
       <c r="X235" s="3">
-        <f>S235/12.049</f>
+        <f t="shared" si="1"/>
         <v>4.0102913104821978</v>
       </c>
       <c r="Y235" s="3">
-        <f t="shared" ref="Y235:Y245" si="10">X235/(496.191*1000)</f>
+        <f t="shared" ref="Y235:Y245" si="13">X235/(496.191*1000)</f>
         <v>8.0821524583924291E-6</v>
       </c>
       <c r="Z235" s="5">
@@ -23118,11 +23119,11 @@
         <v>1.4755126305412945E-5</v>
       </c>
       <c r="AA235" s="3">
-        <f>T235/12.049</f>
+        <f t="shared" si="2"/>
         <v>4.0102913104821978</v>
       </c>
       <c r="AB235" s="3">
-        <f t="shared" ref="AB235:AB245" si="11">AA235/(496.191*1000)</f>
+        <f t="shared" ref="AB235:AB245" si="14">AA235/(496.191*1000)</f>
         <v>8.0821524583924291E-6</v>
       </c>
       <c r="AC235" s="5">
@@ -23133,7 +23134,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="236" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>66</v>
       </c>
@@ -23195,11 +23196,11 @@
         <v>327.55905511811</v>
       </c>
       <c r="U236" s="3">
-        <f>R236/12.049</f>
+        <f t="shared" si="0"/>
         <v>19.553489916175618</v>
       </c>
       <c r="V236" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>3.9407183758221364E-5</v>
       </c>
       <c r="W236" s="5">
@@ -23207,11 +23208,11 @@
         <v>6.3819231591465874E-5</v>
       </c>
       <c r="X236" s="3">
-        <f>S236/12.049</f>
+        <f t="shared" si="1"/>
         <v>11.153063837550087</v>
       </c>
       <c r="Y236" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2.2477360205142953E-5</v>
       </c>
       <c r="Z236" s="5">
@@ -23219,11 +23220,11 @@
         <v>3.72324865105559E-5</v>
       </c>
       <c r="AA236" s="3">
-        <f>T236/12.049</f>
+        <f t="shared" si="2"/>
         <v>27.185580140933688</v>
       </c>
       <c r="AB236" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>5.478853937482479E-5</v>
       </c>
       <c r="AC236" s="5">
@@ -23234,7 +23235,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="237" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>66</v>
       </c>
@@ -23296,11 +23297,11 @@
         <v>802.099801611712</v>
       </c>
       <c r="U237" s="3">
-        <f>R237/12.049</f>
+        <f t="shared" si="0"/>
         <v>58.428085318283678</v>
       </c>
       <c r="V237" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1.1775321462558507E-4</v>
       </c>
       <c r="W237" s="5">
@@ -23308,11 +23309,11 @@
         <v>1.8157244621705096E-4</v>
       </c>
       <c r="X237" s="3">
-        <f>S237/12.049</f>
+        <f t="shared" si="1"/>
         <v>51.234362573298121</v>
       </c>
       <c r="Y237" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1.032553242064006E-4</v>
       </c>
       <c r="Z237" s="5">
@@ -23320,11 +23321,11 @@
         <v>1.404878107169565E-4</v>
       </c>
       <c r="AA237" s="3">
-        <f>T237/12.049</f>
+        <f t="shared" si="2"/>
         <v>66.569823355607269</v>
       </c>
       <c r="AB237" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1.3416169046920898E-4</v>
       </c>
       <c r="AC237" s="5">
@@ -23335,7 +23336,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="238" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>66</v>
       </c>
@@ -23397,11 +23398,11 @@
         <v>245.66929133858201</v>
       </c>
       <c r="U238" s="3">
-        <f>R238/12.049</f>
+        <f t="shared" si="0"/>
         <v>15.301684787119264</v>
       </c>
       <c r="V238" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>3.0838295710964659E-5</v>
       </c>
       <c r="W238" s="5">
@@ -23409,11 +23410,11 @@
         <v>2.1241074192801561E-4</v>
       </c>
       <c r="X238" s="3">
-        <f>S238/12.049</f>
+        <f t="shared" si="1"/>
         <v>10.630264219455224</v>
       </c>
       <c r="Y238" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2.1423734447934817E-5</v>
       </c>
       <c r="Z238" s="5">
@@ -23421,11 +23422,11 @@
         <v>1.619115451648913E-4</v>
       </c>
       <c r="AA238" s="3">
-        <f>T238/12.049</f>
+        <f t="shared" si="2"/>
         <v>20.389185105700225</v>
       </c>
       <c r="AB238" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>4.1091404531118513E-5</v>
       </c>
       <c r="AC238" s="5">
@@ -23436,7 +23437,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="239" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>66</v>
       </c>
@@ -23498,11 +23499,11 @@
         <v>65.091927595964506</v>
       </c>
       <c r="U239" s="3">
-        <f>R239/12.049</f>
+        <f t="shared" si="0"/>
         <v>1.9329404929869698</v>
       </c>
       <c r="V239" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>3.895557341803801E-6</v>
       </c>
       <c r="W239" s="5">
@@ -23510,11 +23511,11 @@
         <v>2.1630629926981941E-4</v>
       </c>
       <c r="X239" s="3">
-        <f>S239/12.049</f>
+        <f t="shared" si="1"/>
         <v>0.17427185755768862</v>
       </c>
       <c r="Y239" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>3.5121930377150858E-7</v>
       </c>
       <c r="Z239" s="5">
@@ -23522,11 +23523,11 @@
         <v>1.6226276446866281E-4</v>
       </c>
       <c r="AA239" s="3">
-        <f>T239/12.049</f>
+        <f t="shared" si="2"/>
         <v>5.4022680385064747</v>
       </c>
       <c r="AB239" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1.0887476875853199E-5</v>
       </c>
       <c r="AC239" s="5">
@@ -23537,7 +23538,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="240" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>66</v>
       </c>
@@ -23599,11 +23600,11 @@
         <v>73.490749569389706</v>
       </c>
       <c r="U240" s="3">
-        <f>R240/12.049</f>
+        <f t="shared" si="0"/>
         <v>3.0873931446593081</v>
       </c>
       <c r="V240" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>6.2221869091928475E-6</v>
       </c>
       <c r="W240" s="5">
@@ -23611,11 +23612,11 @@
         <v>6.2221869091928475E-6</v>
       </c>
       <c r="X240" s="3">
-        <f>S240/12.049</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Y240" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="Z240" s="5">
@@ -23623,11 +23624,11 @@
         <v>0</v>
       </c>
       <c r="AA240" s="3">
-        <f>T240/12.049</f>
+        <f t="shared" si="2"/>
         <v>6.0993235595808537</v>
       </c>
       <c r="AB240" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1.2292289782726518E-5</v>
       </c>
       <c r="AC240" s="5">
@@ -23638,7 +23639,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="241" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>66</v>
       </c>
@@ -23700,11 +23701,11 @@
         <v>73.490749569389706</v>
       </c>
       <c r="U241" s="3">
-        <f>R241/12.049</f>
+        <f t="shared" si="0"/>
         <v>2.8068719395800481</v>
       </c>
       <c r="V241" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>5.6568376685188734E-6</v>
       </c>
       <c r="W241" s="5">
@@ -23712,11 +23713,11 @@
         <v>1.1879024577711722E-5</v>
       </c>
       <c r="X241" s="3">
-        <f>S241/12.049</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Y241" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="Z241" s="5">
@@ -23724,11 +23725,11 @@
         <v>0</v>
       </c>
       <c r="AA241" s="3">
-        <f>T241/12.049</f>
+        <f t="shared" si="2"/>
         <v>6.0993235595808537</v>
       </c>
       <c r="AB241" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1.2292289782726518E-5</v>
       </c>
       <c r="AC241" s="5">
@@ -23739,7 +23740,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="242" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>66</v>
       </c>
@@ -23801,11 +23802,11 @@
         <v>119.685039370078</v>
       </c>
       <c r="U242" s="3">
-        <f>R242/12.049</f>
+        <f t="shared" si="0"/>
         <v>5.8876255290895507</v>
       </c>
       <c r="V242" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1.1865643530595175E-5</v>
       </c>
       <c r="W242" s="5">
@@ -23813,11 +23814,11 @@
         <v>2.3744668108306897E-5</v>
       </c>
       <c r="X242" s="3">
-        <f>S242/12.049</f>
+        <f t="shared" si="1"/>
         <v>1.742670711842319</v>
       </c>
       <c r="Y242" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>3.512096575396005E-6</v>
       </c>
       <c r="Z242" s="5">
@@ -23825,11 +23826,11 @@
         <v>3.512096575396005E-6</v>
       </c>
       <c r="AA242" s="3">
-        <f>T242/12.049</f>
+        <f t="shared" si="2"/>
         <v>9.9331927438026391</v>
       </c>
       <c r="AB242" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>2.0018889386955102E-5</v>
       </c>
       <c r="AC242" s="5">
@@ -23840,7 +23841,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="243" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>66</v>
       </c>
@@ -23902,11 +23903,11 @@
         <v>153.28090397391699</v>
       </c>
       <c r="U243" s="3">
-        <f>R243/12.049</f>
+        <f t="shared" si="0"/>
         <v>9.6671922981160261</v>
       </c>
       <c r="V243" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1.948280460168771E-5</v>
       </c>
       <c r="W243" s="5">
@@ -23914,11 +23915,11 @@
         <v>4.3227472709994606E-5</v>
       </c>
       <c r="X243" s="3">
-        <f>S243/12.049</f>
+        <f t="shared" si="1"/>
         <v>6.9706668927911117</v>
       </c>
       <c r="Y243" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1.4048354147477709E-5</v>
       </c>
       <c r="Z243" s="5">
@@ -23926,11 +23927,11 @@
         <v>1.7560450722873715E-5</v>
       </c>
       <c r="AA243" s="3">
-        <f>T243/12.049</f>
+        <f t="shared" si="2"/>
         <v>12.721462691834757</v>
       </c>
       <c r="AB243" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>2.563823747676753E-5</v>
       </c>
       <c r="AC243" s="5">
@@ -23941,7 +23942,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="244" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>66</v>
       </c>
@@ -24003,11 +24004,11 @@
         <v>100.787401574803</v>
       </c>
       <c r="U244" s="3">
-        <f>R244/12.049</f>
+        <f t="shared" si="0"/>
         <v>5.9341024151381863</v>
       </c>
       <c r="V244" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1.1959310860410984E-5</v>
       </c>
       <c r="W244" s="5">
@@ -24015,11 +24016,11 @@
         <v>5.5186783570405592E-5</v>
       </c>
       <c r="X244" s="3">
-        <f>S244/12.049</f>
+        <f t="shared" si="1"/>
         <v>2.9625258510115779</v>
       </c>
       <c r="Y244" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>5.9705352394774956E-6</v>
       </c>
       <c r="Z244" s="5">
@@ -24027,11 +24028,11 @@
         <v>2.3530985962351212E-5</v>
       </c>
       <c r="AA244" s="3">
-        <f>T244/12.049</f>
+        <f t="shared" si="2"/>
         <v>8.3647938895180509</v>
       </c>
       <c r="AB244" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>1.6858012115330691E-5</v>
       </c>
       <c r="AC244" s="5">
@@ -24042,7 +24043,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="245" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>66</v>
       </c>
@@ -24104,11 +24105,11 @@
         <v>48.2938991756889</v>
       </c>
       <c r="U245" s="3">
-        <f>R245/12.049</f>
+        <f t="shared" si="0"/>
         <v>1.4075856917586522</v>
       </c>
       <c r="V245" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2.8367819887072763E-6</v>
       </c>
       <c r="W245" s="5">
@@ -24116,11 +24117,11 @@
         <v>5.8023565559112871E-5</v>
       </c>
       <c r="X245" s="3">
-        <f>S245/12.049</f>
+        <f t="shared" si="1"/>
         <v>0.87132737863206078</v>
       </c>
       <c r="Y245" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1.7560322106448137E-6</v>
       </c>
       <c r="Z245" s="5">
@@ -24128,11 +24129,11 @@
         <v>2.5287018172996027E-5</v>
       </c>
       <c r="AA245" s="3">
-        <f>T245/12.049</f>
+        <f t="shared" si="2"/>
         <v>4.0081250872013365</v>
       </c>
       <c r="AB245" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>8.0777867538938371E-6</v>
       </c>
       <c r="AC245" s="5">
@@ -24143,7 +24144,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="246" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>41</v>
       </c>
@@ -24235,7 +24236,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="247" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>41</v>
       </c>
@@ -24327,7 +24328,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="248" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>41</v>
       </c>
@@ -24419,7 +24420,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="249" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>41</v>
       </c>
@@ -24511,7 +24512,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="250" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>41</v>
       </c>
@@ -24603,7 +24604,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="251" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>41</v>
       </c>
@@ -24695,7 +24696,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="252" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>41</v>
       </c>
@@ -24787,7 +24788,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="253" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>41</v>
       </c>
@@ -24879,7 +24880,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="254" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>41</v>
       </c>
@@ -24971,7 +24972,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="255" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>41</v>
       </c>
@@ -25063,7 +25064,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="256" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>41</v>
       </c>
@@ -25155,7 +25156,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="257" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>41</v>
       </c>
@@ -25247,7 +25248,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="258" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>41</v>
       </c>
@@ -25339,7 +25340,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="259" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>41</v>
       </c>
@@ -25431,7 +25432,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="260" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>41</v>
       </c>
@@ -25523,7 +25524,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="261" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>41</v>
       </c>
@@ -25615,7 +25616,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="262" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>41</v>
       </c>
@@ -25707,7 +25708,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="263" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>41</v>
       </c>
@@ -25799,7 +25800,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="264" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>41</v>
       </c>
@@ -25891,7 +25892,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="265" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>41</v>
       </c>
@@ -25983,7 +25984,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="266" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>41</v>
       </c>
@@ -26075,7 +26076,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="267" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>41</v>
       </c>
@@ -26167,7 +26168,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="268" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>41</v>
       </c>
@@ -26259,7 +26260,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="269" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>41</v>
       </c>
@@ -26351,7 +26352,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="270" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>41</v>
       </c>
@@ -26443,7 +26444,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="271" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>41</v>
       </c>
@@ -26535,7 +26536,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="272" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>41</v>
       </c>
@@ -26627,7 +26628,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="273" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>41</v>
       </c>
@@ -26719,7 +26720,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="274" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>41</v>
       </c>
@@ -26811,7 +26812,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="275" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>41</v>
       </c>
@@ -26903,7 +26904,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="276" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>41</v>
       </c>
@@ -26995,7 +26996,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="277" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>41</v>
       </c>
@@ -27087,7 +27088,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="278" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>41</v>
       </c>
@@ -27179,7 +27180,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="279" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>41</v>
       </c>
@@ -27271,7 +27272,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="280" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="X280" s="1" t="s">
         <v>24</v>
       </c>
@@ -27279,7 +27280,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="281" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="X281" s="1" t="s">
         <v>24</v>
       </c>
@@ -27287,7 +27288,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="282" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="X282" s="1" t="s">
         <v>24</v>
       </c>
@@ -27295,7 +27296,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="283" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="X283" s="1" t="s">
         <v>24</v>
       </c>
@@ -27303,7 +27304,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="284" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="X284" s="1" t="s">
         <v>24</v>
       </c>
@@ -27311,7 +27312,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="285" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:30" hidden="1" x14ac:dyDescent="0.35">
       <c r="X285" s="1" t="s">
         <v>24</v>
       </c>
@@ -27320,12 +27321,32 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AD285" xr:uid="{81B64A6D-C161-42B0-BDCE-B401913E74B1}"/>
+  <autoFilter ref="A1:AD285" xr:uid="{81B64A6D-C161-42B0-BDCE-B401913E74B1}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Shin"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="6">
+      <filters>
+        <filter val="PO"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002AA8BEAC825CAE4DA772B4C276EF423C" ma:contentTypeVersion="12" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="08e2132e63c6ee1d6b0a0758f6c0554f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="568ff3df-f16a-482d-bb3c-58af1efa1658" xmlns:ns3="13cea704-446d-46be-be94-9e10425fef80" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0ed1ebf33a67d32129b0ef2e0882217b" ns2:_="" ns3:_="">
     <xsd:import namespace="568ff3df-f16a-482d-bb3c-58af1efa1658"/>
@@ -27536,15 +27557,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -27556,6 +27568,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08603937-9A8A-43CD-9840-96EB07A26907}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0109945-5B94-476B-B11F-C8F88FAA444A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27574,14 +27594,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08603937-9A8A-43CD-9840-96EB07A26907}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51F06129-0809-4453-9DBE-E9D618AD8E87}">
   <ds:schemaRefs>

--- a/Input/GoodnessOfFit.Rat.xlsx
+++ b/Input/GoodnessOfFit.Rat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wageningenur4.sharepoint.com/sites/PARCProjectChrysanthi-CChannel/Gedeelde documenten/Chrysa.Nynke_private/CP_L_R/PBK_ZEARALENONE/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="128" documentId="8_{F350443E-DEEE-42B1-90CB-6C99E0D56984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E627F534-C141-41A0-A53B-227552234EF2}"/>
+  <xr:revisionPtr revIDLastSave="164" documentId="8_{F350443E-DEEE-42B1-90CB-6C99E0D56984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C75DC01C-C1AE-475F-9272-AE3C84FAB8CA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7A6CC22C-5805-4016-ACC6-80411866AB2B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6048" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6248" uniqueCount="81">
   <si>
     <t>Author</t>
   </si>
@@ -276,6 +276,9 @@
   </si>
   <si>
     <t>A_cum_min_umol</t>
+  </si>
+  <si>
+    <t>Malli</t>
   </si>
 </sst>
 </file>
@@ -1151,7 +1154,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81B64A6D-C161-42B0-BDCE-B401913E74B1}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:AD285"/>
+  <dimension ref="A1:AD293"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="8.7265625" customWidth="1"/>
@@ -27320,6 +27323,742 @@
         <v>24</v>
       </c>
     </row>
+    <row r="286" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
+        <v>80</v>
+      </c>
+      <c r="B286" t="s">
+        <v>21</v>
+      </c>
+      <c r="C286" t="s">
+        <v>42</v>
+      </c>
+      <c r="D286">
+        <v>0.2</v>
+      </c>
+      <c r="E286">
+        <v>24</v>
+      </c>
+      <c r="F286" t="s">
+        <v>22</v>
+      </c>
+      <c r="G286" t="s">
+        <v>29</v>
+      </c>
+      <c r="H286" t="s">
+        <v>61</v>
+      </c>
+      <c r="I286">
+        <v>3</v>
+      </c>
+      <c r="J286" t="s">
+        <v>24</v>
+      </c>
+      <c r="K286" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L286" t="s">
+        <v>24</v>
+      </c>
+      <c r="M286" t="s">
+        <v>24</v>
+      </c>
+      <c r="N286" t="s">
+        <v>24</v>
+      </c>
+      <c r="O286" t="s">
+        <v>22</v>
+      </c>
+      <c r="P286">
+        <v>0.22153846153846099</v>
+      </c>
+      <c r="Q286" t="s">
+        <v>39</v>
+      </c>
+      <c r="R286" s="1">
+        <v>18.95209681783</v>
+      </c>
+      <c r="S286" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T286" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="U286" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V286" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="W286" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="X286" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y286" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z286" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA286" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB286" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC286" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD286" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="287" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
+        <v>80</v>
+      </c>
+      <c r="B287" t="s">
+        <v>21</v>
+      </c>
+      <c r="C287" t="s">
+        <v>42</v>
+      </c>
+      <c r="D287">
+        <v>0.2</v>
+      </c>
+      <c r="E287">
+        <v>24</v>
+      </c>
+      <c r="F287" t="s">
+        <v>22</v>
+      </c>
+      <c r="G287" t="s">
+        <v>29</v>
+      </c>
+      <c r="H287" t="s">
+        <v>61</v>
+      </c>
+      <c r="I287">
+        <v>3</v>
+      </c>
+      <c r="J287" t="s">
+        <v>24</v>
+      </c>
+      <c r="K287" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L287" t="s">
+        <v>24</v>
+      </c>
+      <c r="M287" t="s">
+        <v>24</v>
+      </c>
+      <c r="N287" t="s">
+        <v>24</v>
+      </c>
+      <c r="O287" t="s">
+        <v>22</v>
+      </c>
+      <c r="P287">
+        <v>0.492306941105769</v>
+      </c>
+      <c r="Q287" t="s">
+        <v>39</v>
+      </c>
+      <c r="R287" s="1">
+        <v>16.706585299866699</v>
+      </c>
+      <c r="S287" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T287" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="U287" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V287" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="W287" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="X287" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y287" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z287" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA287" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB287" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC287" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD287" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="288" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A288" t="s">
+        <v>80</v>
+      </c>
+      <c r="B288" t="s">
+        <v>21</v>
+      </c>
+      <c r="C288" t="s">
+        <v>42</v>
+      </c>
+      <c r="D288">
+        <v>0.2</v>
+      </c>
+      <c r="E288">
+        <v>24</v>
+      </c>
+      <c r="F288" t="s">
+        <v>22</v>
+      </c>
+      <c r="G288" t="s">
+        <v>29</v>
+      </c>
+      <c r="H288" t="s">
+        <v>61</v>
+      </c>
+      <c r="I288">
+        <v>3</v>
+      </c>
+      <c r="J288" t="s">
+        <v>24</v>
+      </c>
+      <c r="K288" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L288" t="s">
+        <v>24</v>
+      </c>
+      <c r="M288" t="s">
+        <v>24</v>
+      </c>
+      <c r="N288" t="s">
+        <v>24</v>
+      </c>
+      <c r="O288" t="s">
+        <v>22</v>
+      </c>
+      <c r="P288">
+        <v>1.0338461538461501</v>
+      </c>
+      <c r="Q288" t="s">
+        <v>39</v>
+      </c>
+      <c r="R288" s="1">
+        <v>8.4431157421074801</v>
+      </c>
+      <c r="S288" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T288" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="U288" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V288" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="W288" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="X288" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y288" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z288" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA288" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB288" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC288" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD288" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="289" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
+        <v>80</v>
+      </c>
+      <c r="B289" t="s">
+        <v>21</v>
+      </c>
+      <c r="C289" t="s">
+        <v>42</v>
+      </c>
+      <c r="D289">
+        <v>0.2</v>
+      </c>
+      <c r="E289">
+        <v>24</v>
+      </c>
+      <c r="F289" t="s">
+        <v>22</v>
+      </c>
+      <c r="G289" t="s">
+        <v>29</v>
+      </c>
+      <c r="H289" t="s">
+        <v>61</v>
+      </c>
+      <c r="I289">
+        <v>3</v>
+      </c>
+      <c r="J289" t="s">
+        <v>24</v>
+      </c>
+      <c r="K289" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L289" t="s">
+        <v>24</v>
+      </c>
+      <c r="M289" t="s">
+        <v>24</v>
+      </c>
+      <c r="N289" t="s">
+        <v>24</v>
+      </c>
+      <c r="O289" t="s">
+        <v>22</v>
+      </c>
+      <c r="P289">
+        <v>1.99384615384615</v>
+      </c>
+      <c r="Q289" t="s">
+        <v>39</v>
+      </c>
+      <c r="R289" s="1">
+        <v>19.221557871053701</v>
+      </c>
+      <c r="S289" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T289" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="U289" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V289" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="W289" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="X289" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y289" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z289" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA289" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB289" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC289" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD289" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="290" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A290" t="s">
+        <v>80</v>
+      </c>
+      <c r="B290" t="s">
+        <v>21</v>
+      </c>
+      <c r="C290" t="s">
+        <v>42</v>
+      </c>
+      <c r="D290">
+        <v>0.2</v>
+      </c>
+      <c r="E290">
+        <v>24</v>
+      </c>
+      <c r="F290" t="s">
+        <v>22</v>
+      </c>
+      <c r="G290" t="s">
+        <v>29</v>
+      </c>
+      <c r="H290" t="s">
+        <v>61</v>
+      </c>
+      <c r="I290">
+        <v>3</v>
+      </c>
+      <c r="J290" t="s">
+        <v>24</v>
+      </c>
+      <c r="K290" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L290" t="s">
+        <v>24</v>
+      </c>
+      <c r="M290" t="s">
+        <v>24</v>
+      </c>
+      <c r="N290" t="s">
+        <v>24</v>
+      </c>
+      <c r="O290" t="s">
+        <v>22</v>
+      </c>
+      <c r="P290">
+        <v>3.9876923076923001</v>
+      </c>
+      <c r="Q290" t="s">
+        <v>39</v>
+      </c>
+      <c r="R290" s="1">
+        <v>16.347301154468902</v>
+      </c>
+      <c r="S290" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T290" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="U290" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V290" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="W290" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="X290" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y290" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z290" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA290" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB290" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC290" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD290" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="291" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A291" t="s">
+        <v>80</v>
+      </c>
+      <c r="B291" t="s">
+        <v>21</v>
+      </c>
+      <c r="C291" t="s">
+        <v>42</v>
+      </c>
+      <c r="D291">
+        <v>0.2</v>
+      </c>
+      <c r="E291">
+        <v>24</v>
+      </c>
+      <c r="F291" t="s">
+        <v>22</v>
+      </c>
+      <c r="G291" t="s">
+        <v>29</v>
+      </c>
+      <c r="H291" t="s">
+        <v>61</v>
+      </c>
+      <c r="I291">
+        <v>3</v>
+      </c>
+      <c r="J291" t="s">
+        <v>24</v>
+      </c>
+      <c r="K291" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L291" t="s">
+        <v>24</v>
+      </c>
+      <c r="M291" t="s">
+        <v>24</v>
+      </c>
+      <c r="N291" t="s">
+        <v>24</v>
+      </c>
+      <c r="O291" t="s">
+        <v>22</v>
+      </c>
+      <c r="P291">
+        <v>5.9569223257211501</v>
+      </c>
+      <c r="Q291" t="s">
+        <v>39</v>
+      </c>
+      <c r="R291" s="1">
+        <v>14.191612728679599</v>
+      </c>
+      <c r="S291" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T291" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="U291" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V291" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="W291" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="X291" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y291" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z291" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA291" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB291" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC291" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD291" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="292" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A292" t="s">
+        <v>80</v>
+      </c>
+      <c r="B292" t="s">
+        <v>21</v>
+      </c>
+      <c r="C292" t="s">
+        <v>42</v>
+      </c>
+      <c r="D292">
+        <v>0.2</v>
+      </c>
+      <c r="E292">
+        <v>24</v>
+      </c>
+      <c r="F292" t="s">
+        <v>22</v>
+      </c>
+      <c r="G292" t="s">
+        <v>29</v>
+      </c>
+      <c r="H292" t="s">
+        <v>61</v>
+      </c>
+      <c r="I292">
+        <v>3</v>
+      </c>
+      <c r="J292" t="s">
+        <v>24</v>
+      </c>
+      <c r="K292" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L292" t="s">
+        <v>24</v>
+      </c>
+      <c r="M292" t="s">
+        <v>24</v>
+      </c>
+      <c r="N292" t="s">
+        <v>24</v>
+      </c>
+      <c r="O292" t="s">
+        <v>22</v>
+      </c>
+      <c r="P292">
+        <v>8.02461463341346</v>
+      </c>
+      <c r="Q292" t="s">
+        <v>39</v>
+      </c>
+      <c r="R292" s="1">
+        <v>10.4191579835484</v>
+      </c>
+      <c r="S292" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T292" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="U292" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V292" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="W292" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="X292" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y292" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z292" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA292" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB292" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC292" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD292" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="293" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A293" t="s">
+        <v>80</v>
+      </c>
+      <c r="B293" t="s">
+        <v>21</v>
+      </c>
+      <c r="C293" t="s">
+        <v>42</v>
+      </c>
+      <c r="D293">
+        <v>0.2</v>
+      </c>
+      <c r="E293">
+        <v>24</v>
+      </c>
+      <c r="F293" t="s">
+        <v>22</v>
+      </c>
+      <c r="G293" t="s">
+        <v>29</v>
+      </c>
+      <c r="H293" t="s">
+        <v>61</v>
+      </c>
+      <c r="I293">
+        <v>3</v>
+      </c>
+      <c r="J293" t="s">
+        <v>24</v>
+      </c>
+      <c r="K293" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L293" t="s">
+        <v>24</v>
+      </c>
+      <c r="M293" t="s">
+        <v>24</v>
+      </c>
+      <c r="N293" t="s">
+        <v>24</v>
+      </c>
+      <c r="O293" t="s">
+        <v>22</v>
+      </c>
+      <c r="P293">
+        <v>23.926153846153799</v>
+      </c>
+      <c r="Q293" t="s">
+        <v>39</v>
+      </c>
+      <c r="R293" s="1">
+        <v>1.3473052661182801</v>
+      </c>
+      <c r="S293" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T293" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="U293" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V293" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="W293" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="X293" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y293" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z293" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA293" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB293" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC293" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD293" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AD285" xr:uid="{81B64A6D-C161-42B0-BDCE-B401913E74B1}">
     <filterColumn colId="0">
@@ -27338,15 +28077,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002AA8BEAC825CAE4DA772B4C276EF423C" ma:contentTypeVersion="12" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="08e2132e63c6ee1d6b0a0758f6c0554f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="568ff3df-f16a-482d-bb3c-58af1efa1658" xmlns:ns3="13cea704-446d-46be-be94-9e10425fef80" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0ed1ebf33a67d32129b0ef2e0882217b" ns2:_="" ns3:_="">
     <xsd:import namespace="568ff3df-f16a-482d-bb3c-58af1efa1658"/>
@@ -27557,6 +28287,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -27568,14 +28307,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08603937-9A8A-43CD-9840-96EB07A26907}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0109945-5B94-476B-B11F-C8F88FAA444A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27594,6 +28325,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08603937-9A8A-43CD-9840-96EB07A26907}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51F06129-0809-4453-9DBE-E9D618AD8E87}">
   <ds:schemaRefs>
